--- a/Har_Ghar_Solar_CRM_10_07_2026.xlsx
+++ b/Har_Ghar_Solar_CRM_10_07_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,35 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00006B3F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00008000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,25 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -154,25 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeadsTable" displayName="SolarLeadsTable" ref="A4:J8" headerRowCount="1">
-  <autoFilter ref="A4:J8"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Customer Name"/>
-    <tableColumn id="3" name="Mobile Number"/>
-    <tableColumn id="4" name="City"/>
-    <tableColumn id="5" name="Monthly Bill"/>
-    <tableColumn id="6" name="Status"/>
-    <tableColumn id="7" name="Follow Note"/>
-    <tableColumn id="8" name="Follow Date"/>
-    <tableColumn id="9" name="Updated By"/>
-    <tableColumn id="10" name="Created Date"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,280 +413,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A4:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>☀ Har Ghar Solar CRM Report</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Mobile Number</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Monthly Bill</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Follow Note</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Follow Date</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>08077181038</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nntnrtnrtnrtntrn</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>₹1000 - ₹3000</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Contacted</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>